--- a/data/trans_orig/P36B11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B11-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2007</t>
+          <t>Población según la frecuencia de consumo de pescado en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21993</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52759</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83703</t>
+          <t>82946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69757</t>
+          <t>69139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99832</t>
+          <t>99749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141915</t>
+          <t>141428</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>351431</t>
+          <t>352805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>406953</t>
+          <t>403391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>394527</t>
+          <t>392100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>443203</t>
+          <t>442819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>759554</t>
+          <t>758904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>835038</t>
+          <t>830577</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200886</t>
+          <t>201275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>252031</t>
+          <t>250577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174313</t>
+          <t>178639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218418</t>
+          <t>224706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>390599</t>
+          <t>389557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>459937</t>
+          <t>457985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31229</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56020</t>
+          <t>58221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89787</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>42029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71815</t>
+          <t>71127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105877</t>
+          <t>109446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150242</t>
+          <t>155326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>461816</t>
+          <t>466918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>528832</t>
+          <t>528087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>517927</t>
+          <t>518639</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>579653</t>
+          <t>581185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1003652</t>
+          <t>1003219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1093546</t>
+          <t>1093493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>330588</t>
+          <t>328586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>394457</t>
+          <t>389720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>292755</t>
+          <t>290249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349554</t>
+          <t>350419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>636380</t>
+          <t>632755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>724796</t>
+          <t>720674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34823</t>
+          <t>35500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>20224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>39610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68026</t>
+          <t>68747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36101</t>
+          <t>35014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41938</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71643</t>
+          <t>72961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35764</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60915</t>
+          <t>61463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86126</t>
+          <t>83676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124623</t>
+          <t>123254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>275482</t>
+          <t>273666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>328741</t>
+          <t>326046</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>303192</t>
+          <t>301246</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>354211</t>
+          <t>354420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>591882</t>
+          <t>587901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>665798</t>
+          <t>667946</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>273402</t>
+          <t>276103</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>327239</t>
+          <t>326046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>252395</t>
+          <t>251865</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>302438</t>
+          <t>304830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>542663</t>
+          <t>543416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>612294</t>
+          <t>616446</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>27260</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42296</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>35755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>44429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70730</t>
+          <t>72013</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75117</t>
+          <t>75452</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112633</t>
+          <t>112693</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70153</t>
+          <t>72446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107833</t>
+          <t>108824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>154694</t>
+          <t>156137</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>207051</t>
+          <t>207480</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>421548</t>
+          <t>419524</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>478579</t>
+          <t>480585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>501720</t>
+          <t>504522</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>567039</t>
+          <t>569477</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>944664</t>
+          <t>941444</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1030863</t>
+          <t>1026615</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322698</t>
+          <t>322506</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>376907</t>
+          <t>379561</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>329660</t>
+          <t>328781</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>389560</t>
+          <t>391261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>669314</t>
+          <t>667892</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>751897</t>
+          <t>752252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18347</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>38574</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>33954</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>37423</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65326</t>
+          <t>63490</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69327</t>
+          <t>67104</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77277</t>
+          <t>79659</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93462</t>
+          <t>91118</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>133681</t>
+          <t>134218</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>258332</t>
+          <t>255562</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>318732</t>
+          <t>318675</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>215991</t>
+          <t>217406</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>275959</t>
+          <t>279537</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>491676</t>
+          <t>489144</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>582750</t>
+          <t>578795</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1571743</t>
+          <t>1571575</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1686602</t>
+          <t>1685085</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1775576</t>
+          <t>1772339</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1893556</t>
+          <t>1884836</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3375403</t>
+          <t>3366839</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3544675</t>
+          <t>3535574</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1181914</t>
+          <t>1173335</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1290554</t>
+          <t>1285845</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1102121</t>
+          <t>1104911</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1208195</t>
+          <t>1212232</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2316651</t>
+          <t>2313757</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2470487</t>
+          <t>2469958</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>59659</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>94283</t>
+          <t>93269</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>68410</t>
+          <t>67886</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>105279</t>
+          <t>104954</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>136328</t>
+          <t>135858</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>185700</t>
+          <t>186991</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2012</t>
+          <t>Población según la frecuencia de consumo de pescado en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23459</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59564</t>
+          <t>58516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93933</t>
+          <t>93779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67336</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>105612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150051</t>
+          <t>148498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>357016</t>
+          <t>354491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>410811</t>
+          <t>409214</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>377105</t>
+          <t>377668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>431361</t>
+          <t>429667</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>749329</t>
+          <t>749142</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>824366</t>
+          <t>821031</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187932</t>
+          <t>187843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237633</t>
+          <t>237769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194224</t>
+          <t>198731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>245844</t>
+          <t>247840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>398254</t>
+          <t>399201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>469019</t>
+          <t>467781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>33852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24956</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28651</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>21959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29521</t>
+          <t>29556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71921</t>
+          <t>73447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110775</t>
+          <t>112160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65249</t>
+          <t>64982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102304</t>
+          <t>100367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146269</t>
+          <t>147543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201034</t>
+          <t>200396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>490700</t>
+          <t>490353</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>556830</t>
+          <t>554623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>490839</t>
+          <t>491613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>559972</t>
+          <t>555135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>999916</t>
+          <t>999628</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1094137</t>
+          <t>1098600</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,74%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>338915</t>
+          <t>339286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>401907</t>
+          <t>405085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>355678</t>
+          <t>357667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>422788</t>
+          <t>419798</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>708278</t>
+          <t>710862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>801075</t>
+          <t>804894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27694</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40250</t>
+          <t>40715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34499</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62871</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>27944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39906</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84765</t>
+          <t>84445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>36746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64069</t>
+          <t>65940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>98402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141707</t>
+          <t>141270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>353980</t>
+          <t>353523</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>411052</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>393095</t>
+          <t>395338</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>451009</t>
+          <t>449644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>764242</t>
+          <t>764507</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>847356</t>
+          <t>845348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>246228</t>
+          <t>245550</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>301725</t>
+          <t>302491</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>239914</t>
+          <t>237751</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>293396</t>
+          <t>292260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>498803</t>
+          <t>501282</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>578615</t>
+          <t>579672</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32794</t>
+          <t>32643</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58801</t>
+          <t>56976</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27883</t>
+          <t>28164</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50272</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>75799</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113567</t>
+          <t>113170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61575</t>
+          <t>61694</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>96896</t>
+          <t>95510</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>144863</t>
+          <t>144606</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>194854</t>
+          <t>197493</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>458525</t>
+          <t>457536</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>520850</t>
+          <t>524954</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>468985</t>
+          <t>470438</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>533989</t>
+          <t>534501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>948689</t>
+          <t>944389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1037766</t>
+          <t>1035496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>287510</t>
+          <t>285749</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>344528</t>
+          <t>346210</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>377328</t>
+          <t>380376</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>442656</t>
+          <t>445295</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>687171</t>
+          <t>687102</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>769774</t>
+          <t>771053</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44168</t>
+          <t>43800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>51517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50480</t>
+          <t>51874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>85642</t>
+          <t>86955</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>64188</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33879</t>
+          <t>33806</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62021</t>
+          <t>61055</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>77643</t>
+          <t>75558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>119288</t>
+          <t>117194</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>292400</t>
+          <t>292433</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>361593</t>
+          <t>362408</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>229692</t>
+          <t>230696</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>292839</t>
+          <t>291768</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>541358</t>
+          <t>543739</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>633974</t>
+          <t>639438</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1719823</t>
+          <t>1721724</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1841708</t>
+          <t>1843551</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1790657</t>
+          <t>1792207</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1912620</t>
+          <t>1915881</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3548641</t>
+          <t>3547058</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3723703</t>
+          <t>3721871</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1112439</t>
+          <t>1109633</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1229749</t>
+          <t>1228108</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1228366</t>
+          <t>1227103</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1343927</t>
+          <t>1354832</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2372098</t>
+          <t>2385516</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2533905</t>
+          <t>2544940</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>76649</t>
+          <t>75400</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>115030</t>
+          <t>116801</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>82934</t>
+          <t>81777</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>121580</t>
+          <t>124120</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>167884</t>
+          <t>168684</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>223099</t>
+          <t>223911</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2016</t>
+          <t>Población según la frecuencia de consumo de pescado en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33166</t>
+          <t>33472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49284</t>
+          <t>47523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79294</t>
+          <t>77083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>46141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77435</t>
+          <t>76541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102227</t>
+          <t>100487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146714</t>
+          <t>143303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>394917</t>
+          <t>394654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>444113</t>
+          <t>445124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>383895</t>
+          <t>383667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>433174</t>
+          <t>434368</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>793596</t>
+          <t>795231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>864522</t>
+          <t>865631</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149191</t>
+          <t>148432</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196183</t>
+          <t>195268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161630</t>
+          <t>162544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209696</t>
+          <t>208070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>325813</t>
+          <t>324764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>389984</t>
+          <t>390077</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26191</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>24222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>45546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59528</t>
+          <t>59560</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93538</t>
+          <t>94553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54192</t>
+          <t>55350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87757</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120786</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>171550</t>
+          <t>173894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>602619</t>
+          <t>600529</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>665420</t>
+          <t>666118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>623333</t>
+          <t>624575</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>687178</t>
+          <t>690224</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1240348</t>
+          <t>1244198</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1331733</t>
+          <t>1331848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>263482</t>
+          <t>259821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>319424</t>
+          <t>321626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251764</t>
+          <t>249126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>310940</t>
+          <t>308378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>530854</t>
+          <t>529869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>615473</t>
+          <t>610973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27713</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40810</t>
+          <t>38364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20251</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83592</t>
+          <t>82859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125915</t>
+          <t>122135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71228</t>
+          <t>71410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108466</t>
+          <t>107188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163326</t>
+          <t>162439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217019</t>
+          <t>218680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>383101</t>
+          <t>385518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>440219</t>
+          <t>440075</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>398500</t>
+          <t>401502</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>455623</t>
+          <t>456807</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>802892</t>
+          <t>802421</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>879878</t>
+          <t>884222</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>191031</t>
+          <t>191018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>241695</t>
+          <t>240688</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>209293</t>
+          <t>210410</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>262439</t>
+          <t>261235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>415351</t>
+          <t>413188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>486018</t>
+          <t>488568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33218</t>
+          <t>32424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>51195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>24754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>29594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49012</t>
+          <t>49395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71844</t>
+          <t>72507</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107109</t>
+          <t>109483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71389</t>
+          <t>70460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107603</t>
+          <t>108070</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>150455</t>
+          <t>152355</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>203723</t>
+          <t>203230</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>561017</t>
+          <t>559910</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>618778</t>
+          <t>619940</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>594584</t>
+          <t>592620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>657711</t>
+          <t>657270</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1176402</t>
+          <t>1173897</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1263123</t>
+          <t>1259271</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>205221</t>
+          <t>208003</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>258146</t>
+          <t>261131</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>265200</t>
+          <t>262821</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>325295</t>
+          <t>324796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>486714</t>
+          <t>488741</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>564576</t>
+          <t>568225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35384</t>
+          <t>34542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>40627</t>
+          <t>39030</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69371</t>
+          <t>70006</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41531</t>
+          <t>40223</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71067</t>
+          <t>69678</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>88985</t>
+          <t>87427</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132024</t>
+          <t>129275</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>293866</t>
+          <t>294174</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>363334</t>
+          <t>365370</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>273663</t>
+          <t>275969</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>338919</t>
+          <t>342641</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>585083</t>
+          <t>585121</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>679549</t>
+          <t>684255</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1997164</t>
+          <t>1996881</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2106136</t>
+          <t>2115320</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2060782</t>
+          <t>2057906</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2181033</t>
+          <t>2179275</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4088609</t>
+          <t>4087412</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4249192</t>
+          <t>4254427</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>857277</t>
+          <t>856596</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>959993</t>
+          <t>959977</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>940353</t>
+          <t>939039</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1052664</t>
+          <t>1050664</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1828432</t>
+          <t>1821751</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1983727</t>
+          <t>1975766</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29000</t>
+          <t>28404</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>57803</t>
+          <t>56248</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>48354</t>
+          <t>48659</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>80548</t>
+          <t>78797</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>84336</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>126384</t>
+          <t>126177</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B11-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82946</t>
+          <t>82908</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>41944</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69139</t>
+          <t>70685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99749</t>
+          <t>102094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141428</t>
+          <t>142690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>352805</t>
+          <t>355281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>403391</t>
+          <t>407989</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>392100</t>
+          <t>390637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>442819</t>
+          <t>442530</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>758904</t>
+          <t>764015</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>830577</t>
+          <t>835592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>201275</t>
+          <t>201468</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250577</t>
+          <t>249980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178639</t>
+          <t>173709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224706</t>
+          <t>222297</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>389557</t>
+          <t>389035</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>457985</t>
+          <t>458423</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18313</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31031</t>
+          <t>29889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>57209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>91424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>41880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71127</t>
+          <t>70947</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109446</t>
+          <t>108804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155326</t>
+          <t>153595</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>466918</t>
+          <t>464257</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>528087</t>
+          <t>528608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>518639</t>
+          <t>518938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>581185</t>
+          <t>580514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1003219</t>
+          <t>1000816</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1093493</t>
+          <t>1094091</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>328586</t>
+          <t>328224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>389720</t>
+          <t>390347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290249</t>
+          <t>288969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>350419</t>
+          <t>350212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>632755</t>
+          <t>635795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>720674</t>
+          <t>726094</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42660</t>
+          <t>43421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39610</t>
+          <t>38595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35014</t>
+          <t>34426</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42507</t>
+          <t>42720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72961</t>
+          <t>72548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35896</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>61078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83676</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>122705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>273666</t>
+          <t>274378</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>326046</t>
+          <t>329186</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>301246</t>
+          <t>302990</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>354420</t>
+          <t>354102</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>587901</t>
+          <t>589285</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>667946</t>
+          <t>665589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>276103</t>
+          <t>271976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>326046</t>
+          <t>327650</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251865</t>
+          <t>254367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>304830</t>
+          <t>303235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>543416</t>
+          <t>539191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>616446</t>
+          <t>615214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>27111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>42130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>15292</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35755</t>
+          <t>35238</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>44462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41936</t>
+          <t>41848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72013</t>
+          <t>71972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75452</t>
+          <t>73774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112693</t>
+          <t>110123</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72446</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>108824</t>
+          <t>107528</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>156137</t>
+          <t>154945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>207480</t>
+          <t>207047</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>419524</t>
+          <t>418587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>480585</t>
+          <t>477540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>504522</t>
+          <t>502982</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>569477</t>
+          <t>568049</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>941444</t>
+          <t>939229</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1026615</t>
+          <t>1028450</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,92%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322506</t>
+          <t>321862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>379561</t>
+          <t>378086</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>328781</t>
+          <t>330575</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>391261</t>
+          <t>391392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>667892</t>
+          <t>667767</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>752252</t>
+          <t>754760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38574</t>
+          <t>38056</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33954</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37423</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>63490</t>
+          <t>66471</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67104</t>
+          <t>67937</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,82 +3475,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>60318</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>45413</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>77473</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>112229</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>93964</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>136185</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>2,05%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>60318</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>46826</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>79659</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>112229</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>91118</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>134218</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>255562</t>
+          <t>255894</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>318675</t>
+          <t>319490</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>217406</t>
+          <t>214090</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>279537</t>
+          <t>274879</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>489144</t>
+          <t>489226</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>578795</t>
+          <t>578789</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1571575</t>
+          <t>1571522</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1685085</t>
+          <t>1687908</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1772339</t>
+          <t>1769230</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1884836</t>
+          <t>1885215</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3366839</t>
+          <t>3378998</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3535574</t>
+          <t>3539825</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1173335</t>
+          <t>1182232</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1285845</t>
+          <t>1288637</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1104911</t>
+          <t>1102980</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1212232</t>
+          <t>1213222</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2313757</t>
+          <t>2313020</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2469958</t>
+          <t>2469425</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>58785</t>
+          <t>60618</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>93269</t>
+          <t>95392</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>67886</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>102185</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>135858</t>
+          <t>135977</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>186991</t>
+          <t>186452</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23716</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58516</t>
+          <t>58985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93779</t>
+          <t>92652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>38140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66996</t>
+          <t>64969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105612</t>
+          <t>105608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148498</t>
+          <t>149402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>354491</t>
+          <t>355465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>409214</t>
+          <t>409772</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>377668</t>
+          <t>376377</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>429667</t>
+          <t>431494</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>749142</t>
+          <t>747808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>821031</t>
+          <t>825573</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187843</t>
+          <t>188528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237769</t>
+          <t>237296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198731</t>
+          <t>198552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>247840</t>
+          <t>248500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>399201</t>
+          <t>398303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>467781</t>
+          <t>468317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33852</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>27402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27729</t>
+          <t>28820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53478</t>
+          <t>53948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>21593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29556</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73447</t>
+          <t>73078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112160</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64982</t>
+          <t>65365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100367</t>
+          <t>101722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147543</t>
+          <t>146458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200396</t>
+          <t>201784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>490353</t>
+          <t>491458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>554623</t>
+          <t>556309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>491613</t>
+          <t>494941</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>555135</t>
+          <t>557884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>999628</t>
+          <t>1000771</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1098600</t>
+          <t>1090687</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>339286</t>
+          <t>339105</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>405085</t>
+          <t>401341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>357667</t>
+          <t>356593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>419798</t>
+          <t>420926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>710862</t>
+          <t>714943</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>804894</t>
+          <t>803747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40715</t>
+          <t>40199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>62081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27944</t>
+          <t>26080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>41165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52762</t>
+          <t>51687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84445</t>
+          <t>84500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36746</t>
+          <t>36762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65940</t>
+          <t>65149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98402</t>
+          <t>98078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141270</t>
+          <t>139954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>353523</t>
+          <t>354755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>410242</t>
+          <t>411337</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>395338</t>
+          <t>392286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>449644</t>
+          <t>448834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>764507</t>
+          <t>762831</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>845348</t>
+          <t>843574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>245550</t>
+          <t>243676</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>302491</t>
+          <t>301372</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>237751</t>
+          <t>241699</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>292260</t>
+          <t>295695</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>501282</t>
+          <t>505684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>579672</t>
+          <t>584223</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>14352</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32643</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>29327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>59954</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28164</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>29603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>49661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75799</t>
+          <t>75290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113170</t>
+          <t>114095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61694</t>
+          <t>60943</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95510</t>
+          <t>95784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>144606</t>
+          <t>147221</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>197493</t>
+          <t>198644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>457536</t>
+          <t>461404</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>524954</t>
+          <t>521527</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>470438</t>
+          <t>468938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>534501</t>
+          <t>534969</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>944389</t>
+          <t>949866</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1035496</t>
+          <t>1041217</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>285749</t>
+          <t>287922</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>346210</t>
+          <t>348100</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>380376</t>
+          <t>379899</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>445295</t>
+          <t>445300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>687102</t>
+          <t>682662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>771053</t>
+          <t>767860</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19359</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>41888</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51517</t>
+          <t>50808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,47 +6922,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>66510</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>50533</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>85171</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>66510</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>51874</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>86955</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>35594</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>66283</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33806</t>
+          <t>33660</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61055</t>
+          <t>60808</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75558</t>
+          <t>73849</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>117194</t>
+          <t>117282</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>292433</t>
+          <t>291632</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>362408</t>
+          <t>362602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>230696</t>
+          <t>230409</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>291768</t>
+          <t>292826</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>543739</t>
+          <t>543259</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>639438</t>
+          <t>635296</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1721724</t>
+          <t>1719096</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1843551</t>
+          <t>1841992</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1792207</t>
+          <t>1789030</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1915881</t>
+          <t>1911620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3547058</t>
+          <t>3550224</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3721871</t>
+          <t>3723151</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1109633</t>
+          <t>1112180</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1228108</t>
+          <t>1226160</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1227103</t>
+          <t>1230377</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1354832</t>
+          <t>1349391</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2385516</t>
+          <t>2367576</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2544940</t>
+          <t>2540961</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>75400</t>
+          <t>75243</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>116801</t>
+          <t>116882</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>81777</t>
+          <t>80732</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>124120</t>
+          <t>122748</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>168684</t>
+          <t>171033</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>223911</t>
+          <t>224583</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>48653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77083</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>46970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76541</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100487</t>
+          <t>101584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143303</t>
+          <t>144391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>394654</t>
+          <t>394255</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>445124</t>
+          <t>444540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>383667</t>
+          <t>385709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>434368</t>
+          <t>434932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>795231</t>
+          <t>786814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>865631</t>
+          <t>864736</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148432</t>
+          <t>148379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195268</t>
+          <t>196242</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162544</t>
+          <t>161800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208070</t>
+          <t>207060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>324764</t>
+          <t>324620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390077</t>
+          <t>394072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>14250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>25696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24222</t>
+          <t>23548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21958</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45546</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59560</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94553</t>
+          <t>94049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55350</t>
+          <t>54269</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88851</t>
+          <t>88427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>121686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173894</t>
+          <t>169622</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>600529</t>
+          <t>601005</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666118</t>
+          <t>665938</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>624575</t>
+          <t>623370</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>690224</t>
+          <t>684944</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1244198</t>
+          <t>1240169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1331848</t>
+          <t>1335471</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>259821</t>
+          <t>260708</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321626</t>
+          <t>319737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>249126</t>
+          <t>251517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>308378</t>
+          <t>307989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>529869</t>
+          <t>529815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>610973</t>
+          <t>614136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38364</t>
+          <t>39859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29628</t>
+          <t>30228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82859</t>
+          <t>84747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122135</t>
+          <t>126570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>70974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107188</t>
+          <t>109289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162439</t>
+          <t>165097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>218680</t>
+          <t>217653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>385518</t>
+          <t>384805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>440075</t>
+          <t>441267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>401502</t>
+          <t>400379</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>456807</t>
+          <t>457293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>802421</t>
+          <t>800231</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>884222</t>
+          <t>881250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,25%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>191018</t>
+          <t>192100</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>240688</t>
+          <t>241632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>210410</t>
+          <t>211433</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>261235</t>
+          <t>265922</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>413188</t>
+          <t>414413</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>488568</t>
+          <t>489482</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32424</t>
+          <t>31306</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>26062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51195</t>
+          <t>50678</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24754</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29594</t>
+          <t>29783</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25744</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49395</t>
+          <t>48867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72507</t>
+          <t>70443</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109483</t>
+          <t>106659</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70460</t>
+          <t>69298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>108070</t>
+          <t>106705</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>152355</t>
+          <t>151841</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>203230</t>
+          <t>202296</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>559910</t>
+          <t>559111</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>619940</t>
+          <t>617163</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>592620</t>
+          <t>592352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>657270</t>
+          <t>659853</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1173897</t>
+          <t>1173201</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1259271</t>
+          <t>1263492</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,95%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>208003</t>
+          <t>204208</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>261131</t>
+          <t>260321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>262821</t>
+          <t>261999</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>324796</t>
+          <t>322554</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>488741</t>
+          <t>487261</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>568225</t>
+          <t>565117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>35044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39030</t>
+          <t>40774</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70006</t>
+          <t>69674</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40223</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69678</t>
+          <t>70696</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87427</t>
+          <t>87706</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>129275</t>
+          <t>129138</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>294174</t>
+          <t>296152</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>365370</t>
+          <t>365685</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>275969</t>
+          <t>272758</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>342641</t>
+          <t>338438</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>585121</t>
+          <t>589745</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>684255</t>
+          <t>686372</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1996881</t>
+          <t>2000160</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2115320</t>
+          <t>2115317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2057906</t>
+          <t>2063920</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2179275</t>
+          <t>2183014</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4087412</t>
+          <t>4091007</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4254427</t>
+          <t>4264969</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,6%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>856596</t>
+          <t>855251</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>959977</t>
+          <t>957416</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>939039</t>
+          <t>939261</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1050664</t>
+          <t>1051359</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1821751</t>
+          <t>1814407</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1975766</t>
+          <t>1976490</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>56248</t>
+          <t>54184</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>48323</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>78797</t>
+          <t>81969</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>84877</t>
+          <t>83598</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>126177</t>
+          <t>123601</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
